--- a/import_data/dados_efluentes.xlsx
+++ b/import_data/dados_efluentes.xlsx
@@ -1,28 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dedel\Documents\Python Scripts\App_Mosaic\import_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97DFF9C-7891-4B21-AECF-933289D8D6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258D86CA-2DB8-4A77-97B2-C4DF16967B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{035A0FDB-F6DB-411C-836F-BDCE2CEF2366}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="9" xr2:uid="{035A0FDB-F6DB-411C-836F-BDCE2CEF2366}"/>
   </bookViews>
   <sheets>
     <sheet name="Unidade medicaos" sheetId="3" r:id="rId1"/>
-    <sheet name="Parametros" sheetId="2" r:id="rId2"/>
-    <sheet name="Unidade empresarials" sheetId="4" r:id="rId3"/>
-    <sheet name="Ponto monitoramentos" sheetId="1" r:id="rId4"/>
-    <sheet name="Monitoramento efluentes" sheetId="5" r:id="rId5"/>
+    <sheet name="Unidade empresarials" sheetId="4" r:id="rId2"/>
+    <sheet name="Programa" sheetId="6" r:id="rId3"/>
+    <sheet name="Subcategoria" sheetId="7" r:id="rId4"/>
+    <sheet name="Subcategoria unidade" sheetId="8" r:id="rId5"/>
+    <sheet name="Parametros" sheetId="2" r:id="rId6"/>
+    <sheet name="Ponto monitoramentos" sheetId="1" r:id="rId7"/>
+    <sheet name="Ruidos" sheetId="9" r:id="rId8"/>
+    <sheet name="Efluentes liquidos" sheetId="5" r:id="rId9"/>
+    <sheet name="Emissoes" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ponto monitoramentos'!$A$1:$G$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ponto monitoramentos'!$A$1:$G$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -176,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="364">
   <si>
     <t>Nome</t>
   </si>
@@ -870,9 +876,6 @@
     <t>Unidade medicao</t>
   </si>
   <si>
-    <t>Categoria</t>
-  </si>
-  <si>
     <t>Requisito</t>
   </si>
   <si>
@@ -1002,9 +1005,6 @@
     <t>0.5</t>
   </si>
   <si>
-    <t>Inorgânicos</t>
-  </si>
-  <si>
     <t>0.2</t>
   </si>
   <si>
@@ -1056,9 +1056,6 @@
     <t>1.2</t>
   </si>
   <si>
-    <t>Orgânicos</t>
-  </si>
-  <si>
     <t>0.07</t>
   </si>
   <si>
@@ -1198,6 +1195,87 @@
   </si>
   <si>
     <t>22</t>
+  </si>
+  <si>
+    <t>Subcategoria</t>
+  </si>
+  <si>
+    <t>Emissões</t>
+  </si>
+  <si>
+    <t>Efluentes Liquidos</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>Materiais sedimentáveis</t>
+  </si>
+  <si>
+    <t>Resolução CONAMA n° 430/2012</t>
+  </si>
+  <si>
+    <t>Limite max</t>
+  </si>
+  <si>
+    <t>Sanitário</t>
+  </si>
+  <si>
+    <t>Resolução CONAMA n° 430/2010</t>
+  </si>
+  <si>
+    <t>Pluvial</t>
+  </si>
+  <si>
+    <t>Outros parâmetros especificados na LO</t>
+  </si>
+  <si>
+    <t>DQO</t>
+  </si>
+  <si>
+    <t>Outros - Toxicidade Aguda FTbl para Vibrio fischeri</t>
+  </si>
+  <si>
+    <t>Outros - Toxicidade Aguda FTd para Daphnia magna</t>
+  </si>
+  <si>
+    <t>Outros - Toxidade Crônica FTd para Scenedesmus subspicatus</t>
+  </si>
+  <si>
+    <t>Outros - pH</t>
+  </si>
+  <si>
+    <t>Outros - Materiais sedimentáveis</t>
+  </si>
+  <si>
+    <t>mililitro por litro</t>
+  </si>
+  <si>
+    <t>Programa</t>
+  </si>
+  <si>
+    <t>Tipo ruido</t>
+  </si>
+  <si>
+    <t>Diurno</t>
+  </si>
+  <si>
+    <t>Noturno</t>
+  </si>
+  <si>
+    <t>Tipo emissoes</t>
+  </si>
+  <si>
+    <t>Atmosférica</t>
+  </si>
+  <si>
+    <t>Qualidade do Ar</t>
+  </si>
+  <si>
+    <t>Admensional</t>
+  </si>
+  <si>
+    <t>ml/l</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1291,6 +1369,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1352,7 +1442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1439,100 +1529,14 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Ruim" xfId="1" builtinId="27"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA7A9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1965,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25114D3F-D5DB-447A-9479-BFB57BBE9173}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
@@ -1976,20 +1980,20 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" t="s">
         <v>138</v>
@@ -1997,34 +2001,50 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>305</v>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B9" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2032,925 +2052,246 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44207D10-2223-4163-9736-622835CE4657}">
-  <dimension ref="A1:F45"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D109BB-3A35-4004-A121-B472BD6D2011}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="B1" t="s">
-        <v>228</v>
+        <v>327</v>
       </c>
       <c r="C1" t="s">
-        <v>229</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="E1" t="s">
-        <v>231</v>
+        <v>329</v>
       </c>
       <c r="F1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+      <c r="G1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G2" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G3" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G4" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B5" t="s">
         <v>235</v>
       </c>
-      <c r="B2">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B3">
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G5" s="2">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5">
-        <v>240</v>
-      </c>
-      <c r="C5" t="s">
-        <v>302</v>
-      </c>
-      <c r="D5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G6" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G7" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>157</v>
       </c>
-      <c r="B6">
+      <c r="B8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E6" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D7" t="s">
-        <v>244</v>
-      </c>
-      <c r="E7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>247</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D8" t="s">
-        <v>244</v>
-      </c>
-      <c r="E8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F8" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>300</v>
-      </c>
-      <c r="D9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E9" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D10" t="s">
-        <v>244</v>
-      </c>
-      <c r="E10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D11" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>251</v>
-      </c>
-      <c r="B12">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D12" t="s">
-        <v>244</v>
-      </c>
-      <c r="E12" t="s">
-        <v>245</v>
-      </c>
-      <c r="F12" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13" t="s">
-        <v>273</v>
-      </c>
-      <c r="C13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" t="s">
-        <v>274</v>
-      </c>
-      <c r="E13" t="s">
-        <v>245</v>
-      </c>
-      <c r="F13" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>300</v>
-      </c>
-      <c r="D14" t="s">
-        <v>274</v>
-      </c>
-      <c r="E14" t="s">
-        <v>245</v>
-      </c>
-      <c r="F14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>254</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>300</v>
-      </c>
-      <c r="D15" t="s">
-        <v>274</v>
-      </c>
-      <c r="E15" t="s">
-        <v>245</v>
-      </c>
-      <c r="F15" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>255</v>
-      </c>
-      <c r="B16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" t="s">
-        <v>300</v>
-      </c>
-      <c r="D16" t="s">
-        <v>274</v>
-      </c>
-      <c r="E16" t="s">
-        <v>245</v>
-      </c>
-      <c r="F16" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>256</v>
-      </c>
-      <c r="B17" t="s">
-        <v>273</v>
-      </c>
-      <c r="C17" t="s">
-        <v>300</v>
-      </c>
-      <c r="D17" t="s">
-        <v>274</v>
-      </c>
-      <c r="E17" t="s">
-        <v>245</v>
-      </c>
-      <c r="F17" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>257</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>300</v>
-      </c>
-      <c r="D18" t="s">
-        <v>274</v>
-      </c>
-      <c r="E18" t="s">
-        <v>245</v>
-      </c>
-      <c r="F18" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>258</v>
-      </c>
-      <c r="B19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" t="s">
-        <v>300</v>
-      </c>
-      <c r="D19" t="s">
-        <v>274</v>
-      </c>
-      <c r="E19" t="s">
-        <v>245</v>
-      </c>
-      <c r="F19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>300</v>
-      </c>
-      <c r="D20" t="s">
-        <v>274</v>
-      </c>
-      <c r="E20" t="s">
-        <v>245</v>
-      </c>
-      <c r="F20" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>260</v>
-      </c>
-      <c r="B21" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" t="s">
-        <v>300</v>
-      </c>
-      <c r="D21" t="s">
-        <v>274</v>
-      </c>
-      <c r="E21" t="s">
-        <v>245</v>
-      </c>
-      <c r="F21" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>261</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>300</v>
-      </c>
-      <c r="D22" t="s">
-        <v>274</v>
-      </c>
-      <c r="E22" t="s">
-        <v>245</v>
-      </c>
-      <c r="F22" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>262</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>300</v>
-      </c>
-      <c r="D23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E23" t="s">
-        <v>245</v>
-      </c>
-      <c r="F23" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>263</v>
-      </c>
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>300</v>
-      </c>
-      <c r="D24" t="s">
-        <v>274</v>
-      </c>
-      <c r="E24" t="s">
-        <v>245</v>
-      </c>
-      <c r="F24" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>264</v>
-      </c>
-      <c r="B25">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>300</v>
-      </c>
-      <c r="D25" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" t="s">
-        <v>245</v>
-      </c>
-      <c r="F25" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>265</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>300</v>
-      </c>
-      <c r="D26" t="s">
-        <v>274</v>
-      </c>
-      <c r="E26" t="s">
-        <v>245</v>
-      </c>
-      <c r="F26" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>266</v>
-      </c>
-      <c r="B27" t="s">
-        <v>277</v>
-      </c>
-      <c r="C27" t="s">
-        <v>300</v>
-      </c>
-      <c r="D27" t="s">
-        <v>274</v>
-      </c>
-      <c r="E27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F27" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>267</v>
-      </c>
-      <c r="B28">
+        <v>157</v>
+      </c>
+      <c r="B9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G9" s="2">
         <v>2</v>
       </c>
-      <c r="C28" t="s">
-        <v>300</v>
-      </c>
-      <c r="D28" t="s">
-        <v>274</v>
-      </c>
-      <c r="E28" t="s">
-        <v>245</v>
-      </c>
-      <c r="F28" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>268</v>
-      </c>
-      <c r="B29">
-        <v>20</v>
-      </c>
-      <c r="C29" t="s">
-        <v>300</v>
-      </c>
-      <c r="D29" t="s">
-        <v>274</v>
-      </c>
-      <c r="E29" t="s">
-        <v>245</v>
-      </c>
-      <c r="F29" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>269</v>
-      </c>
-      <c r="B30" t="s">
-        <v>276</v>
-      </c>
-      <c r="C30" t="s">
-        <v>300</v>
-      </c>
-      <c r="D30" t="s">
-        <v>274</v>
-      </c>
-      <c r="E30" t="s">
-        <v>245</v>
-      </c>
-      <c r="F30" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>270</v>
-      </c>
-      <c r="B31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C31" t="s">
-        <v>300</v>
-      </c>
-      <c r="D31" t="s">
-        <v>274</v>
-      </c>
-      <c r="E31" t="s">
-        <v>245</v>
-      </c>
-      <c r="F31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>271</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>300</v>
-      </c>
-      <c r="D32" t="s">
-        <v>274</v>
-      </c>
-      <c r="E32" t="s">
-        <v>245</v>
-      </c>
-      <c r="F32" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>272</v>
-      </c>
-      <c r="B33">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>300</v>
-      </c>
-      <c r="D33" t="s">
-        <v>274</v>
-      </c>
-      <c r="E33" t="s">
-        <v>245</v>
-      </c>
-      <c r="F33" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>279</v>
-      </c>
-      <c r="B34" t="s">
-        <v>291</v>
-      </c>
-      <c r="C34" t="s">
-        <v>300</v>
-      </c>
-      <c r="D34" t="s">
-        <v>292</v>
-      </c>
-      <c r="E34" t="s">
-        <v>245</v>
-      </c>
-      <c r="F34" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>280</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>300</v>
-      </c>
-      <c r="D35" t="s">
-        <v>292</v>
-      </c>
-      <c r="E35" t="s">
-        <v>245</v>
-      </c>
-      <c r="F35" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>281</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>300</v>
-      </c>
-      <c r="D36" t="s">
-        <v>292</v>
-      </c>
-      <c r="E36" t="s">
-        <v>245</v>
-      </c>
-      <c r="F36" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>282</v>
-      </c>
-      <c r="B37" t="s">
-        <v>293</v>
-      </c>
-      <c r="C37" t="s">
-        <v>300</v>
-      </c>
-      <c r="D37" t="s">
-        <v>292</v>
-      </c>
-      <c r="E37" t="s">
-        <v>245</v>
-      </c>
-      <c r="F37" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>283</v>
-      </c>
-      <c r="B38" t="s">
-        <v>294</v>
-      </c>
-      <c r="C38" t="s">
-        <v>300</v>
-      </c>
-      <c r="D38" t="s">
-        <v>292</v>
-      </c>
-      <c r="E38" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>284</v>
-      </c>
-      <c r="B39" t="s">
-        <v>273</v>
-      </c>
-      <c r="C39" t="s">
-        <v>300</v>
-      </c>
-      <c r="D39" t="s">
-        <v>292</v>
-      </c>
-      <c r="E39" t="s">
-        <v>245</v>
-      </c>
-      <c r="F39" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>285</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>300</v>
-      </c>
-      <c r="D40" t="s">
-        <v>292</v>
-      </c>
-      <c r="E40" t="s">
-        <v>245</v>
-      </c>
-      <c r="F40" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>286</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>300</v>
-      </c>
-      <c r="D41" t="s">
-        <v>292</v>
-      </c>
-      <c r="E41" t="s">
-        <v>245</v>
-      </c>
-      <c r="F41" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>287</v>
-      </c>
-      <c r="B42" t="s">
-        <v>291</v>
-      </c>
-      <c r="C42" t="s">
-        <v>300</v>
-      </c>
-      <c r="D42" t="s">
-        <v>292</v>
-      </c>
-      <c r="E42" t="s">
-        <v>245</v>
-      </c>
-      <c r="F42" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>288</v>
-      </c>
-      <c r="B43" t="s">
-        <v>295</v>
-      </c>
-      <c r="C43" t="s">
-        <v>300</v>
-      </c>
-      <c r="D43" t="s">
-        <v>292</v>
-      </c>
-      <c r="E43" t="s">
-        <v>245</v>
-      </c>
-      <c r="F43" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>289</v>
-      </c>
-      <c r="B44">
-        <v>100</v>
-      </c>
-      <c r="C44" t="s">
-        <v>300</v>
-      </c>
-      <c r="D44" t="s">
-        <v>244</v>
-      </c>
-      <c r="E44" t="s">
-        <v>245</v>
-      </c>
-      <c r="F44" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45">
-        <v>120</v>
-      </c>
-      <c r="C45" t="s">
-        <v>300</v>
-      </c>
-      <c r="D45" t="s">
-        <v>244</v>
-      </c>
-      <c r="E45" t="s">
-        <v>245</v>
-      </c>
-      <c r="F45" t="s">
-        <v>246</v>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABBBAB72-0C5F-4592-9440-8DECD961AB59}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2960,13 +2301,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2974,10 +2315,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2985,10 +2326,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2996,10 +2337,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3007,10 +2348,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -3018,10 +2359,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3029,10 +2370,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -3040,10 +2381,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -3051,10 +2392,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -3062,10 +2403,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -3073,10 +2414,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3084,10 +2425,10 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C12" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -3095,10 +2436,44 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C13" t="s">
-        <v>329</v>
+        <v>326</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003A6D69-EDA4-477E-AE45-01159393B3C6}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -3107,6 +2482,3475 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D77E1-E3CC-4DC7-8338-DAD2D9F15B47}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>340</v>
+      </c>
+      <c r="B6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DEB7F0D-5EBB-45A5-A59A-F6FDE69A6FA9}">
+  <dimension ref="A1:B85"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>236</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>340</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>340</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>340</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>340</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>340</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>340</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>340</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>340</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>340</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>340</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>340</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>344</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>344</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>344</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>344</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>344</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>344</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>344</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>344</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>344</v>
+      </c>
+      <c r="B70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>344</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>344</v>
+      </c>
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>344</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>346</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>346</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>346</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>346</v>
+      </c>
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>346</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>346</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>346</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>346</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>346</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>346</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>346</v>
+      </c>
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>346</v>
+      </c>
+      <c r="B85" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44207D10-2223-4163-9736-622835CE4657}">
+  <dimension ref="A1:G129"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="30">
+        <v>70</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="30">
+        <v>60</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="31">
+        <v>75</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="31">
+        <v>240</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="31">
+        <v>2</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="30">
+        <v>60</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="30">
+        <v>0</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B9" s="30">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="30">
+        <v>20</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="30">
+        <v>50</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="30">
+        <v>6</v>
+      </c>
+      <c r="C12" s="30">
+        <v>9</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="30">
+        <v>40</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="30">
+        <v>5</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="30">
+        <v>5</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="30">
+        <v>1</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="30">
+        <v>1</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" s="30">
+        <v>1</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B24" s="30">
+        <v>4</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="B25" s="30">
+        <v>5</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" s="30">
+        <v>10</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="30">
+        <v>1</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B29" s="30">
+        <v>2</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30" s="30">
+        <v>20</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B33" s="30">
+        <v>1</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="B34" s="30">
+        <v>5</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G34" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B36" s="30">
+        <v>1</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G36" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B37" s="30">
+        <v>1</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G38" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G39" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B41" s="30">
+        <v>1</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G41" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B42" s="30">
+        <v>1</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F42" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G43" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="F44" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G44" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B45" s="31">
+        <v>100</v>
+      </c>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F45" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B46" s="31">
+        <v>120</v>
+      </c>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F46" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="31">
+        <v>60</v>
+      </c>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="E47" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F47" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="B48" s="31">
+        <v>0</v>
+      </c>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="B49" s="31">
+        <v>0</v>
+      </c>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E49" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F49" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B50" s="31">
+        <v>20</v>
+      </c>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F50" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B51" s="31">
+        <v>50</v>
+      </c>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E51" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F51" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G51" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B52" s="31">
+        <v>6</v>
+      </c>
+      <c r="C52" s="31">
+        <v>9</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="E52" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G52" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="B53" s="31">
+        <v>40</v>
+      </c>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G53" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B55" s="31">
+        <v>5</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E55" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G55" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="B56" s="31">
+        <v>5</v>
+      </c>
+      <c r="C56" s="31"/>
+      <c r="D56" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G56" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E57" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G57" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E58" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F58" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G58" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1</v>
+      </c>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E59" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F59" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G59" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E60" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G60" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1</v>
+      </c>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E61" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F61" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G61" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="31"/>
+      <c r="D62" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G62" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1</v>
+      </c>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E63" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F63" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G63" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" s="31">
+        <v>4</v>
+      </c>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E64" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G64" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="B65" s="31">
+        <v>5</v>
+      </c>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E65" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F65" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G65" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="B66" s="31">
+        <v>10</v>
+      </c>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E66" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G66" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="B67" s="31">
+        <v>1</v>
+      </c>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E67" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E68" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F68" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G68" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B69" s="31">
+        <v>2</v>
+      </c>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E69" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F69" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G69" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="31">
+        <v>20</v>
+      </c>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F70" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G70" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E71" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F71" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G71" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E72" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F72" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G72" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" s="31">
+        <v>1</v>
+      </c>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E73" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F73" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="B74" s="31">
+        <v>5</v>
+      </c>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E74" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E75" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F75" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B76" s="31">
+        <v>1</v>
+      </c>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E76" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F76" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G76" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B77" s="31">
+        <v>1</v>
+      </c>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E77" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F77" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E79" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F79" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G79" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C80" s="31"/>
+      <c r="D80" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F80" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B81" s="31">
+        <v>1</v>
+      </c>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F81" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B82" s="31">
+        <v>1</v>
+      </c>
+      <c r="C82" s="31"/>
+      <c r="D82" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F82" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C83" s="31"/>
+      <c r="D83" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F83" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G83" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="C84" s="31"/>
+      <c r="D84" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="F84" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G84" s="31" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="B85" s="30">
+        <v>60</v>
+      </c>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G85" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B86" s="30">
+        <v>0</v>
+      </c>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G86" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B87" s="30">
+        <v>0</v>
+      </c>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="G87" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B88" s="30">
+        <v>20</v>
+      </c>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G88" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B89" s="30">
+        <v>50</v>
+      </c>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E89" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G89" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="B90" s="30">
+        <v>6</v>
+      </c>
+      <c r="C90" s="30">
+        <v>9</v>
+      </c>
+      <c r="D90" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E90" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F90" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G90" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B91" s="30">
+        <v>40</v>
+      </c>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F91" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G91" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B92" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E92" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F92" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G92" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B93" s="30">
+        <v>5</v>
+      </c>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E93" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G93" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B94" s="30">
+        <v>5</v>
+      </c>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E94" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F94" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G94" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E95" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G95" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E96" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G96" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B97" s="30">
+        <v>1</v>
+      </c>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E97" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G97" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B98" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E98" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F98" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G98" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="B99" s="30">
+        <v>1</v>
+      </c>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E99" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G99" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="B100" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E100" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F100" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G100" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B101" s="30">
+        <v>1</v>
+      </c>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G101" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B102" s="30">
+        <v>4</v>
+      </c>
+      <c r="C102" s="30"/>
+      <c r="D102" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E102" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G102" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="B103" s="30">
+        <v>5</v>
+      </c>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G103" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B104" s="30">
+        <v>10</v>
+      </c>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E104" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F104" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G104" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="B105" s="30">
+        <v>1</v>
+      </c>
+      <c r="C105" s="30"/>
+      <c r="D105" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E105" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G105" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="B106" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="C106" s="30"/>
+      <c r="D106" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F106" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G106" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B107" s="30">
+        <v>2</v>
+      </c>
+      <c r="C107" s="30"/>
+      <c r="D107" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E107" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F107" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G107" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="B108" s="30">
+        <v>20</v>
+      </c>
+      <c r="C108" s="30"/>
+      <c r="D108" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E108" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F108" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G108" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B109" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="C109" s="30"/>
+      <c r="D109" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E109" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G109" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="B110" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="C110" s="30"/>
+      <c r="D110" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E110" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F110" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G110" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B111" s="30">
+        <v>1</v>
+      </c>
+      <c r="C111" s="30"/>
+      <c r="D111" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E111" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G111" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="B112" s="30">
+        <v>5</v>
+      </c>
+      <c r="C112" s="30"/>
+      <c r="D112" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E112" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F112" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G112" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B113" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E113" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G113" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B114" s="30">
+        <v>1</v>
+      </c>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E114" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G114" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B115" s="30">
+        <v>1</v>
+      </c>
+      <c r="C115" s="30"/>
+      <c r="D115" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E115" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F115" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G115" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="B116" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="C116" s="30"/>
+      <c r="D116" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E116" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F116" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G116" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B117" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="C117" s="30"/>
+      <c r="D117" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E117" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G117" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B118" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E118" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F118" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G118" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B119" s="30">
+        <v>1</v>
+      </c>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E119" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F119" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G119" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B120" s="30">
+        <v>1</v>
+      </c>
+      <c r="C120" s="30"/>
+      <c r="D120" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E120" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F120" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G120" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B121" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="C121" s="30"/>
+      <c r="D121" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E121" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G121" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="B122" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E122" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F122" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="G122" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="B123" s="30">
+        <v>50</v>
+      </c>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E123" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G123" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B124" s="30">
+        <v>300</v>
+      </c>
+      <c r="C124" s="30"/>
+      <c r="D124" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E124" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F124" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G124" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="B125" s="30">
+        <v>8</v>
+      </c>
+      <c r="C125" s="30"/>
+      <c r="D125" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="E125" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F125" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G125" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="B126" s="30">
+        <v>8</v>
+      </c>
+      <c r="C126" s="30"/>
+      <c r="D126" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="E126" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F126" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G126" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B127" s="30">
+        <v>8</v>
+      </c>
+      <c r="C127" s="30"/>
+      <c r="D127" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="E127" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F127" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G127" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="B128" s="30">
+        <v>5</v>
+      </c>
+      <c r="C128" s="30">
+        <v>9</v>
+      </c>
+      <c r="D128" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E128" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F128" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G128" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B129" s="30">
+        <v>1</v>
+      </c>
+      <c r="C129" s="30"/>
+      <c r="D129" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="E129" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="F129" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="G129" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CDB5A-20E9-4C13-A9F2-BC156CEDD77B}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G182"/>
@@ -3420,7 +6264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>169</v>
       </c>
@@ -3443,7 +6287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>170</v>
       </c>
@@ -3466,7 +6310,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>171</v>
       </c>
@@ -3489,7 +6333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>172</v>
       </c>
@@ -3512,7 +6356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>173</v>
       </c>
@@ -3535,7 +6379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>174</v>
       </c>
@@ -3558,7 +6402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>175</v>
       </c>
@@ -3581,7 +6425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>176</v>
       </c>
@@ -3604,7 +6448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>177</v>
       </c>
@@ -3627,7 +6471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>178</v>
       </c>
@@ -3650,7 +6494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>179</v>
       </c>
@@ -3673,7 +6517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>180</v>
       </c>
@@ -3696,7 +6540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>181</v>
       </c>
@@ -3704,7 +6548,7 @@
         <v>39</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D26" s="5">
         <v>0</v>
@@ -3719,7 +6563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>182</v>
       </c>
@@ -3727,7 +6571,7 @@
         <v>40</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D27" s="5">
         <v>0</v>
@@ -3742,7 +6586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>183</v>
       </c>
@@ -3750,7 +6594,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D28" s="5">
         <v>0</v>
@@ -3765,7 +6609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>184</v>
       </c>
@@ -3773,7 +6617,7 @@
         <v>41</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D29" s="5">
         <v>0</v>
@@ -5030,7 +7874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>203</v>
       </c>
@@ -5053,7 +7897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>204</v>
       </c>
@@ -5076,7 +7920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>205</v>
       </c>
@@ -5099,7 +7943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>206</v>
       </c>
@@ -5122,7 +7966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>206</v>
       </c>
@@ -5145,7 +7989,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>206</v>
       </c>
@@ -5168,7 +8012,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>207</v>
       </c>
@@ -5191,7 +8035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>207</v>
       </c>
@@ -5214,7 +8058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>207</v>
       </c>
@@ -5237,7 +8081,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>208</v>
       </c>
@@ -5260,7 +8104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>208</v>
       </c>
@@ -5283,7 +8127,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>208</v>
       </c>
@@ -5306,15 +8150,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D96" s="5">
         <v>0</v>
@@ -5329,7 +8173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>209</v>
       </c>
@@ -5352,7 +8196,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>26</v>
       </c>
@@ -5375,7 +8219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>26</v>
       </c>
@@ -5398,7 +8242,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>210</v>
       </c>
@@ -5444,7 +8288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>210</v>
       </c>
@@ -5467,7 +8311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>211</v>
       </c>
@@ -5490,7 +8334,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A104" s="20" t="s">
         <v>169</v>
       </c>
@@ -5498,7 +8342,7 @@
         <v>94</v>
       </c>
       <c r="C104" s="29" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D104" s="11">
         <v>7172109</v>
@@ -5507,13 +8351,13 @@
         <v>744460</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G104" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>169</v>
       </c>
@@ -5530,13 +8374,13 @@
         <v>744832</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>171</v>
       </c>
@@ -5553,13 +8397,13 @@
         <v>744557</v>
       </c>
       <c r="F106" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G106" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>172</v>
       </c>
@@ -5576,13 +8420,13 @@
         <v>744377</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G107" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>173</v>
       </c>
@@ -5599,7 +8443,7 @@
         <v>744689</v>
       </c>
       <c r="F108" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G108" s="15" t="s">
         <v>13</v>
@@ -5622,7 +8466,7 @@
         <v>749062</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G109" s="7" t="s">
         <v>14</v>
@@ -5645,7 +8489,7 @@
         <v>748932</v>
       </c>
       <c r="F110" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G110" s="7" t="s">
         <v>14</v>
@@ -5668,7 +8512,7 @@
         <v>749056</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G111" s="7" t="s">
         <v>14</v>
@@ -5691,7 +8535,7 @@
         <v>748935</v>
       </c>
       <c r="F112" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G112" s="7" t="s">
         <v>14</v>
@@ -5714,7 +8558,7 @@
         <v>748984</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G113" s="7" t="s">
         <v>14</v>
@@ -7284,7 +10128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="23" t="s">
         <v>176</v>
       </c>
@@ -7311,13 +10155,13 @@
   <autoFilter ref="A1:G182" xr:uid="{2B3CDB5A-20E9-4C13-A9F2-BC156CEDD77B}">
     <filterColumn colId="6">
       <filters>
-        <filter val="Uberaba"/>
+        <filter val="Paranaguá 2"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A2:G182">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Não informado">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Não informado">
       <formula>NOT(ISERROR(SEARCH("Não informado",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7326,738 +10170,658 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1E6AEF-376A-4ED8-917F-C3F0E8D087A6}">
-  <dimension ref="A1:I38"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA10EBEC-154A-47A0-B3A8-5E00992F9550}">
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1" t="s">
         <v>330</v>
       </c>
+      <c r="G1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G2" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G3" s="2">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G4" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G5" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G6" s="2">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G7" s="2">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G8" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4">
+        <v>45806</v>
+      </c>
+      <c r="G9" s="2">
+        <v>50.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Não informado">
+      <formula>NOT(ISERROR(SEARCH("Não informado",D2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1E6AEF-376A-4ED8-917F-C3F0E8D087A6}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>334</v>
+      </c>
       <c r="B1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G1" t="s">
         <v>331</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>332</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>333</v>
       </c>
-      <c r="F1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="H1" t="s">
-        <v>336</v>
-      </c>
-      <c r="I1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F2" s="2">
-        <v>62</v>
+      <c r="E2" s="3"/>
+      <c r="F2" s="26">
+        <v>45658</v>
+      </c>
+      <c r="G2" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F3" s="2">
-        <v>60.3</v>
+      <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="26">
+        <v>45717</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F4" s="2">
-        <v>61.9</v>
+      <c r="A4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G4" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F5" s="2">
-        <v>61.9</v>
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="26">
+        <v>45839</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F6" s="2">
-        <v>54.8</v>
+      <c r="A6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="26">
+        <v>45901</v>
+      </c>
+      <c r="G6" s="2">
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F7" s="2">
-        <v>50.1</v>
+      <c r="A7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="26">
+        <v>45992</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F8" s="2">
-        <v>61</v>
+      <c r="A8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="26">
+        <v>45778</v>
+      </c>
+      <c r="G8" s="2">
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4">
-        <v>45806</v>
-      </c>
-      <c r="F9" s="2">
-        <v>50.1</v>
+      <c r="A9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="26">
+        <v>45809</v>
+      </c>
+      <c r="G9" s="2">
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F10" s="2">
-        <v>135</v>
+      <c r="A10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="26">
+        <v>45839</v>
+      </c>
+      <c r="G10" s="2">
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F11" s="2">
-        <v>180</v>
+      <c r="A11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="26">
+        <v>45870</v>
+      </c>
+      <c r="G11" s="2">
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F12" s="2">
-        <v>150</v>
+      <c r="A12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="26">
+        <v>45901</v>
+      </c>
+      <c r="G12" s="2">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>236</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F13" s="2">
-        <v>60</v>
+        <v>340</v>
+      </c>
+      <c r="B13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="26">
+        <v>45931</v>
+      </c>
+      <c r="G13" s="2">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F14" s="2">
-        <v>65</v>
+        <v>340</v>
+      </c>
+      <c r="B14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="26">
+        <v>45962</v>
+      </c>
+      <c r="G14" s="2">
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>236</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F15" s="2">
-        <v>55</v>
+        <v>340</v>
+      </c>
+      <c r="B15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="26">
+        <v>45992</v>
+      </c>
+      <c r="G15" s="2">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F16" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+      <c r="B16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="26">
+        <v>46023</v>
+      </c>
+      <c r="G16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F17" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+      <c r="B17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="26">
+        <v>46054</v>
+      </c>
+      <c r="G17" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F18" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+      <c r="B18" t="s">
+        <v>288</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="26">
+        <v>46082</v>
+      </c>
+      <c r="G18" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>248</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="26">
-        <v>45658</v>
-      </c>
-      <c r="F19" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="26">
-        <v>45717</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F21" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>248</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="26">
-        <v>45839</v>
-      </c>
-      <c r="F22" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>248</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="26">
-        <v>45901</v>
-      </c>
-      <c r="F23" s="2">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>248</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="26">
-        <v>45992</v>
-      </c>
-      <c r="F24" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>290</v>
-      </c>
-      <c r="B25" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B19" t="s">
+        <v>288</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="26">
-        <v>45778</v>
-      </c>
-      <c r="F25" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>290</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="26">
-        <v>45809</v>
-      </c>
-      <c r="F26" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>290</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="26">
-        <v>45839</v>
-      </c>
-      <c r="F27" s="2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>290</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="D19" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="26">
-        <v>45870</v>
-      </c>
-      <c r="F28" s="2">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>243</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="26">
-        <v>45901</v>
-      </c>
-      <c r="F29" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>243</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="26">
-        <v>45931</v>
-      </c>
-      <c r="F30" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>243</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="26">
-        <v>45962</v>
-      </c>
-      <c r="F31" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>243</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="26">
-        <v>45992</v>
-      </c>
-      <c r="F32" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>290</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="26">
-        <v>46023</v>
-      </c>
-      <c r="F33" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>290</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="26">
-        <v>46054</v>
-      </c>
-      <c r="F34" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>290</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="26">
-        <v>46082</v>
-      </c>
-      <c r="F35" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>290</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="26">
+      <c r="E19" s="3"/>
+      <c r="F19" s="26">
         <v>46113</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G19" s="2">
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C38" s="27"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C25:C28">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C25)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C32">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C33:C36">
+  <conditionalFormatting sqref="D8:D19">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Não informado">
-      <formula>NOT(ISERROR(SEARCH("Não informado",C33)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Não informado",D8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
